--- a/werkervaring.xlsx
+++ b/werkervaring.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hogeschoolpxl-my.sharepoint.com/personal/12503773_student_pxl_be/Documents/Documents/GitHub/portfolio-IlyaTripspxl/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hogeschoolpxl-my.sharepoint.com/personal/12503773_student_pxl_be/Documents/Documents/GitHub/publiek-bestanden-to-share/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="8_{D25C5BA8-D74B-4BE0-B548-9B4675EFEC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60DC3561-BE32-4CA1-B841-ADBBBEB4F622}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{D25C5BA8-D74B-4BE0-B548-9B4675EFEC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F259506-578C-4246-A391-CCC6A74F83FB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3380EFB5-9B0B-4E41-83DA-8D6134DF02D9}"/>
   </bookViews>
@@ -127,7 +127,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -135,17 +135,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -493,36 +509,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -531,21 +547,21 @@
       <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -554,21 +570,21 @@
       <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="4">
         <v>45474</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -577,10 +593,10 @@
       <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="4">
         <v>45479</v>
       </c>
     </row>
@@ -591,20 +607,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="15c03bca-7036-4cc4-8a95-bccae7a37a41" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="15c03bca-7036-4cc4-8a95-bccae7a37a41" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -790,6 +806,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0656B8AA-2262-4AAA-B447-A57BEC59C507}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FC3129B-3FAB-4E7B-862F-B673536C177B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -801,14 +825,6 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0656B8AA-2262-4AAA-B447-A57BEC59C507}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/werkervaring.xlsx
+++ b/werkervaring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hogeschoolpxl-my.sharepoint.com/personal/12503773_student_pxl_be/Documents/Documents/GitHub/publiek-bestanden-to-share/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{D25C5BA8-D74B-4BE0-B548-9B4675EFEC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F259506-578C-4246-A391-CCC6A74F83FB}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{D25C5BA8-D74B-4BE0-B548-9B4675EFEC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{960C2677-B4BF-45B3-A9DE-A29E3D5A07BA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3380EFB5-9B0B-4E41-83DA-8D6134DF02D9}"/>
   </bookViews>
